--- a/ig/DM-AOUT-2026/CodeSystem-tre-r392-type-act-smsse-regulee.xlsx
+++ b/ig/DM-AOUT-2026/CodeSystem-tre-r392-type-act-smsse-regulee.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14859" uniqueCount="9928">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14871" uniqueCount="9936">
   <si>
     <t>Property</t>
   </si>
@@ -121,7 +121,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>4910</t>
+    <t>4914</t>
   </si>
   <si>
     <t>Code</t>
@@ -29798,6 +29798,30 @@
   </si>
   <si>
     <t>ASOCR/960/11/811</t>
+  </si>
+  <si>
+    <t>81061</t>
+  </si>
+  <si>
+    <t>ASOCR/246/21/824</t>
+  </si>
+  <si>
+    <t>81062</t>
+  </si>
+  <si>
+    <t>ASOCR/246/21/835</t>
+  </si>
+  <si>
+    <t>81063</t>
+  </si>
+  <si>
+    <t>ASOCR/247/21/824</t>
+  </si>
+  <si>
+    <t>81064</t>
+  </si>
+  <si>
+    <t>ASOCR/247/21/835</t>
   </si>
 </sst>
 </file>
@@ -30425,7 +30449,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D4911"/>
+  <dimension ref="A1:D4915"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -89362,6 +89386,54 @@
       </c>
       <c r="D4911" s="2"/>
     </row>
+    <row r="4912">
+      <c r="A4912" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="B4912" t="s" s="2">
+        <v>9928</v>
+      </c>
+      <c r="C4912" t="s" s="2">
+        <v>9929</v>
+      </c>
+      <c r="D4912" s="2"/>
+    </row>
+    <row r="4913">
+      <c r="A4913" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="B4913" t="s" s="2">
+        <v>9930</v>
+      </c>
+      <c r="C4913" t="s" s="2">
+        <v>9931</v>
+      </c>
+      <c r="D4913" s="2"/>
+    </row>
+    <row r="4914">
+      <c r="A4914" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="B4914" t="s" s="2">
+        <v>9932</v>
+      </c>
+      <c r="C4914" t="s" s="2">
+        <v>9933</v>
+      </c>
+      <c r="D4914" s="2"/>
+    </row>
+    <row r="4915">
+      <c r="A4915" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="B4915" t="s" s="2">
+        <v>9934</v>
+      </c>
+      <c r="C4915" t="s" s="2">
+        <v>9935</v>
+      </c>
+      <c r="D4915" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
